--- a/R/Input/DATA.xlsx
+++ b/R/Input/DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ojaulime\OneDrive - Banco de la República\Documents\Research\MP transmission in Colombia\Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia\R\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancodelarepublica-my.sharepoint.com/personal/ojaulime_banrep_gov_co/Documents/Documents/Research/MP transmission in Colombia/Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia/R/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A7BA06-15EE-486E-B896-9040FC5EED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{61A7BA06-15EE-486E-B896-9040FC5EED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F26BCA97-EBD6-4726-BEB4-81E64A647CF2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5935AB3E-80CE-4E87-9EB4-B18D2E64BDED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -516,9 +516,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DADDA8-F05A-4B81-9CDB-818A1AD50DCA}">
   <dimension ref="A1:AH259"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>36892</v>
       </c>
@@ -648,7 +648,7 @@
         <v>6.3130434782608796E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>36923</v>
       </c>
@@ -685,7 +685,7 @@
         <v>-1.4550000000000118E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>36951</v>
       </c>
@@ -722,7 +722,7 @@
         <v>-8.2499999999999934E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>36982</v>
       </c>
@@ -760,7 +760,7 @@
         <v>-1.2171428571428555E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>37012</v>
       </c>
@@ -797,7 +797,7 @@
         <v>-1.5552173913043477E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>37043</v>
       </c>
@@ -834,7 +834,7 @@
         <v>-1.7285714285714293E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>37073</v>
       </c>
@@ -871,7 +871,7 @@
         <v>-3.6390909090909106E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>37104</v>
       </c>
@@ -908,7 +908,7 @@
         <v>-4.2800000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>37135</v>
       </c>
@@ -945,7 +945,7 @@
         <v>-4.3389999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>37165</v>
       </c>
@@ -982,7 +982,7 @@
         <v>-5.2556521739130453E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>37196</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>-6.5645454545454535E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>37226</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>-4.0528571428571428E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>37257</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>-3.3530434782608705E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>37288</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>-1.9664999999999995E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>37316</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>-1.6323809523809525E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>37347</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>-1.5513636363636361E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>37377</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>-2.3252173913043475E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>37408</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>-3.8199999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>37438</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>-4.2578260869565232E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>37469</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>-3.2827272727272705E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>37500</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>-2.1804761904761896E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>37530</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>-2.6126086956521744E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>37561</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>-3.263809523809523E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>37591</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>-3.49E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>37622</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>-3.1478260869565206E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>37653</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>-2.6575000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>37681</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>-2.1438095238095242E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>37712</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>-2.0140909090909084E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>37742</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>-1.9445454545454544E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>37773</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>-1.8642857142857142E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>37803</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>-1.9330434782608701E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>37834</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>-1.992857142857142E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>37865</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>-1.7954545454545459E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>37895</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>-1.5239130434782609E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>37926</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>-1.0650000000000007E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>37956</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>-9.6260869565217427E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37987</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>-1.0750000000000003E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38018</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>-1.1555000000000003E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>38047</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>38078</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>5.498492E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>38108</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>-2.1428079999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>38139</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>2.048608E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>38169</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1.8538300000000001E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>38200</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>-3.776566E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>38231</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>-1.8236659999999998E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>38261</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>-1.1853829999999999E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>38292</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1.36775E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>38322</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>-0.1222645</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>38353</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>4.5591700000000004E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>38384</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>1.36775E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>38412</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>0.11486080999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>38443</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>5.4710000000000002E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>38473</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>2.2645E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>38504</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>-5.5011599999999997E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>38534</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>-2.826683E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>38565</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>4.5592000000000001E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>38596</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>-0.23819141999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>38626</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>2.860209E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>38657</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>-1.8236699999999999E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>38687</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>3.1914159999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>38718</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>3.1914199999999999E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>38749</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>38777</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>5.9269199999999996E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>38808</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>7.2976819999999998E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>38838</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>-0.11150349</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>38869</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>1.5440829999999999E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>38899</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>-9.8828319999999997E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>38930</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>8.6171700000000004E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>38961</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>7.2720419999999994E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>38991</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>5.8236660000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>39022</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>-2.591183E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>39052</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>0.10091182999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>39083</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>2.305567E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>39114</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>-0.11212531000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>39142</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>-3.2370080000000002E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>39173</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>-4.529E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>39203</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>-0.23709169999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>39234</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>-5.8933899999999997E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>39264</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>5.5911830000000003E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>39295</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>-5.674825E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>39326</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>-0.23797336999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>39356</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>-0.25985736999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>39387</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>0.11908816999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>39417</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>0.23253254000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>39448</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>-4.2562299999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>39479</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>5.9226639999999997E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>39508</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>0.32610652000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>39539</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>0.36944381999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>39569</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>-0.44944381999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>39600</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>-0.44350611000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>39630</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0.46301308000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>39661</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>-4.4953279999999998E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>39692</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>-6.0536899999999996E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>39722</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>-0.49770323999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>39753</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>-0.38327783999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>39783</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>0.15606513999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>39814</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>-0.47338358000000003</v>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>39845</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>-0.54739097999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>39873</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>-0.51314877000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>39904</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>-0.55107950000000006</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>39934</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>-0.50324221000000002</v>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>39965</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>-0.63880201999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>39995</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>1.3102050000000001E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>40026</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>6.4171309999999995E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>40057</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>-0.24067295</v>
       </c>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>40087</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>-1.2484429999999999E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>40118</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>-0.35513646999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>40148</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>0.12279754</v>
       </c>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>40179</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>0.11314877</v>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>40210</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>0.10201721</v>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>40238</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>40269</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>-0.27829754000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>40299</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>40330</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>-3.0679919999999999E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>40360</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>-3.2695490000000001E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>40391</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>0.19299957000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>40422</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>-0.15866063999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>40452</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>-2.303115E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>40483</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>0.11330941</v>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>40513</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>-4.4633199999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>40544</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>-2.235123E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>40575</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>9.36332E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>40603</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>0.24520900000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>40634</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>2.351557E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>40664</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>5.9281970000000003E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>40695</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>6.0484429999999999E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>40725</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>2.2031149999999999E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>40756</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>-0.23957581</v>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>40787</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>-4.789098E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>40817</v>
       </c>
@@ -9160,7 +9160,7 @@
         <v>-5.9437700000000003E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>40848</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>4.510902E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>40878</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>-3.4757789999999997E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>40909</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>0.11464877</v>
       </c>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>40940</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>8.6711070000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>40969</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>-1.2164339999999999E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>41000</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>-1.2437699999999999E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>41030</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>-0.23711719000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>41061</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>-2.275779E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>41091</v>
       </c>
@@ -10087,7 +10087,7 @@
         <v>-0.18792212999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>41122</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>-4.3515570000000003E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>41153</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>-8.2380309999999998E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>41183</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>1.7195490000000001E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>41214</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>-0.22312088999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>41244</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>-3.877336E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>41275</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>1.8468849999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>41306</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>0.12164506999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>41334</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>-0.24754302</v>
       </c>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>41365</v>
       </c>
@@ -11014,7 +11014,7 @@
         <v>0.17684753</v>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>41395</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>0.16510695</v>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>0.20424875000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>41456</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>0.14866925</v>
       </c>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>41487</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>-0.14827826999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>41518</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>41548</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>1.72664E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>41579</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>41609</v>
       </c>
@@ -11838,7 +11838,7 @@
         <v>9.9688499999999996E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>41640</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>-5.3045100000000001E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>41671</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>-3.9844299999999997E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>41699</v>
       </c>
@@ -12147,7 +12147,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>41730</v>
       </c>
@@ -12250,7 +12250,7 @@
         <v>0.12378893000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>41760</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>2.0359829999999999E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>41791</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>-2.44377E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>41821</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>6.5617620000000002E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>41852</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>5.6788930000000001E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>41883</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>9.1799199999999994E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>41913</v>
       </c>
@@ -12880,7 +12880,7 @@
         <v>-2.3993029999999999E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>41944</v>
       </c>
@@ -12986,7 +12986,7 @@
         <v>5.1557000000000003E-4</v>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>41974</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>-5.0954909999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>42005</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>2.9688499999999999E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>42036</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>2.5778999999999998E-4</v>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>42064</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>-4.95328E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>42095</v>
       </c>
@@ -13516,7 +13516,7 @@
         <v>1.403975E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>42125</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>-2.181311E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>42156</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>-1.069549E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>42186</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>7.4930300000000003E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>42217</v>
       </c>
@@ -13940,7 +13940,7 @@
         <v>-5.9726639999999998E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>42248</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>7.5437699999999996E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>42278</v>
       </c>
@@ -14152,7 +14152,7 @@
         <v>8.803975E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>42309</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>-7.4226639999999997E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>42339</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>-3.927336E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>42370</v>
       </c>
@@ -14470,7 +14470,7 @@
         <v>-4.3242210000000003E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>42401</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>-4.5211069999999999E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>42430</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>2.9679919999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>42461</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>0.10966434</v>
       </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>42491</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>-1.8288929999999998E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>42522</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>-5.4844300000000002E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>42552</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>-6.5172099999999998E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>42583</v>
       </c>
@@ -15212,7 +15212,7 @@
         <v>-5.7133200000000002E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>42614</v>
       </c>
@@ -15318,7 +15318,7 @@
         <v>-2.4688499999999999E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>42644</v>
       </c>
@@ -15424,7 +15424,7 @@
         <v>1.5155699999999999E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>42675</v>
       </c>
@@ -15530,7 +15530,7 @@
         <v>4.7110700000000004E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>42705</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>-0.10871107000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>42736</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>9.5875409999999994E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>42767</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>-7.9695489999999994E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>42795</v>
       </c>
@@ -15954,7 +15954,7 @@
         <v>4.9257790000000003E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>42826</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>-2.814877E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>42856</v>
       </c>
@@ -16166,7 +16166,7 @@
         <v>4.8757790000000002E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>42887</v>
       </c>
@@ -16272,7 +16272,7 @@
         <v>-2.2313110000000001E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>42917</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>3.5015570000000003E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>42948</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>1.6726640000000001E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>42979</v>
       </c>
@@ -16590,7 +16590,7 @@
         <v>3.7211069999999999E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>43009</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>-0.10117992000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>43040</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>-3.2179920000000001E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>43070</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>43101</v>
       </c>
@@ -17014,7 +17014,7 @@
         <v>-6.0288929999999998E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>43132</v>
       </c>
@@ -17120,7 +17120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>43160</v>
       </c>
@@ -17226,7 +17226,7 @@
         <v>3.2515570000000001E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>43191</v>
       </c>
@@ -17332,7 +17332,7 @@
         <v>1.4532799999999999E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>43221</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>43252</v>
       </c>
@@ -17544,7 +17544,7 @@
         <v>-1.808647E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>43282</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>-2.152418E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>43313</v>
       </c>
@@ -17756,7 +17756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>43344</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>43374</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>43405</v>
       </c>
@@ -18074,7 +18074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>43435</v>
       </c>
@@ -18180,7 +18180,7 @@
         <v>5.9377039999999999E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>43466</v>
       </c>
@@ -18286,7 +18286,7 @@
         <v>1.0390979999999999E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>43497</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>43525</v>
       </c>
@@ -18498,7 +18498,7 @@
         <v>-6.1799200000000002E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>43556</v>
       </c>
@@ -18604,7 +18604,7 @@
         <v>9.6487699999999992E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>43586</v>
       </c>
@@ -18710,7 +18710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>43617</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>8.6799200000000007E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>43647</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>5.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>43678</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>43709</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>2.4221E-4</v>
       </c>
     </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>43739</v>
       </c>
@@ -19240,7 +19240,7 @@
         <v>9.2761060000000006E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>43770</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>43800</v>
       </c>
@@ -19452,123 +19452,123 @@
         <v>7.6447940000000006E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N230" s="3"/>
       <c r="O230" s="3"/>
     </row>
-    <row r="231" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N231" s="3"/>
       <c r="O231" s="3"/>
     </row>
-    <row r="232" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N232" s="3"/>
       <c r="O232" s="3"/>
     </row>
-    <row r="233" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N233" s="3"/>
       <c r="O233" s="3"/>
     </row>
-    <row r="234" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N234" s="3"/>
       <c r="O234" s="3"/>
     </row>
-    <row r="235" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N235" s="3"/>
       <c r="O235" s="3"/>
     </row>
-    <row r="236" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N236" s="3"/>
       <c r="O236" s="3"/>
     </row>
-    <row r="237" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N237" s="3"/>
       <c r="O237" s="3"/>
     </row>
-    <row r="238" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N238" s="3"/>
       <c r="O238" s="3"/>
     </row>
-    <row r="239" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N239" s="3"/>
       <c r="O239" s="3"/>
     </row>
-    <row r="240" spans="1:34" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:34" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N240" s="3"/>
       <c r="O240" s="3"/>
     </row>
-    <row r="241" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="241" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N241" s="3"/>
       <c r="O241" s="3"/>
     </row>
-    <row r="242" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="242" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N242" s="3"/>
       <c r="O242" s="3"/>
     </row>
-    <row r="243" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="243" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N243" s="3"/>
       <c r="O243" s="3"/>
     </row>
-    <row r="244" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="244" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N244" s="3"/>
       <c r="O244" s="3"/>
     </row>
-    <row r="245" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="245" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
     </row>
-    <row r="246" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="246" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N246" s="3"/>
       <c r="O246" s="3"/>
     </row>
-    <row r="247" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="247" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N247" s="3"/>
       <c r="O247" s="3"/>
     </row>
-    <row r="248" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="248" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N248" s="3"/>
       <c r="O248" s="3"/>
     </row>
-    <row r="249" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="249" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N249" s="3"/>
       <c r="O249" s="3"/>
     </row>
-    <row r="250" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="250" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
     </row>
-    <row r="251" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="251" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N251" s="3"/>
       <c r="O251" s="3"/>
     </row>
-    <row r="252" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="252" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N252" s="3"/>
       <c r="O252" s="3"/>
     </row>
-    <row r="253" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="253" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N253" s="3"/>
       <c r="O253" s="3"/>
     </row>
-    <row r="254" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="254" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N254" s="3"/>
       <c r="O254" s="3"/>
     </row>
-    <row r="255" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="255" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N255" s="3"/>
       <c r="O255" s="3"/>
     </row>
-    <row r="256" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="256" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N256" s="3"/>
       <c r="O256" s="3"/>
     </row>
-    <row r="257" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="257" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N257" s="3"/>
       <c r="O257" s="3"/>
     </row>
-    <row r="258" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="258" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N258" s="3"/>
       <c r="O258" s="3"/>
     </row>
-    <row r="259" spans="14:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="259" spans="14:15" ht="15.5" x14ac:dyDescent="0.4">
       <c r="N259" s="3"/>
       <c r="O259" s="3"/>
     </row>
